--- a/04_DESIGN_TABLES/DesignTable_6602_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6602_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,6 +3161,270 @@
       <c r="CB10" t="inlineStr">
         <is>
           <t>6602-24-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6602-32-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="n">
+        <v>37</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>37</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>6602-32-32-32-FG</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>Female Swivel Run Tee, 2 1/2-12 JIC x 2 1/2-12 (female 37deg JIC swivel) x 2 1/2-12 JIC</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>6602</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>2 1/2-12 JIC</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>2 1/2-12 JIC</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>Air-Way s194 only (double-pass 39 rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; ASSUMED for a tee); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p057-t02: agrees on M1@DRIVE, C3HEX@HEX, Y@HEX, D1@BORE, D2@BORE, D3@BORE | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>6602-32-32-32-FG</t>
         </is>
       </c>
     </row>
